--- a/Asesorias.xlsx
+++ b/Asesorias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/087993982d207e1c/Documentos/Servicio Social/Que ti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{6C7DCCC3-FD91-4193-A8FC-BB4518FAFD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BE56189-A663-4331-8754-7B12B3B50477}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{6C7DCCC3-FD91-4193-A8FC-BB4518FAFD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{163B97E9-2088-4B1E-9791-2111AF861759}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{942D3E2B-9E87-4F98-A7E3-9A8E0167E555}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Día</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Uriel Josué</t>
   </si>
   <si>
-    <t>Ecuaciones</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -112,9 +109,6 @@
   </si>
   <si>
     <t>N.C del asesor</t>
-  </si>
-  <si>
-    <t>Ninguna</t>
   </si>
   <si>
     <t>Creado por:</t>
@@ -141,13 +135,22 @@
     <t>Diagramas</t>
   </si>
   <si>
-    <t>Davidcito</t>
+    <t>Necesita prácticar con ejercicios</t>
   </si>
   <si>
-    <t>No pasa, no da ni una</t>
+    <t xml:space="preserve">Santiago Giovanni Rodriguez Palacios </t>
   </si>
   <si>
-    <t>Rodrigo Vera Perez</t>
+    <t>Números Imaginarios</t>
+  </si>
+  <si>
+    <t>Necesita prácticar con ejercicios y concentrarse</t>
+  </si>
+  <si>
+    <t>Investigación de operaciones</t>
+  </si>
+  <si>
+    <t>Brandon Erick López Cervantes</t>
   </si>
 </sst>
 </file>
@@ -806,11 +809,11 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -821,7 +824,7 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -830,13 +833,13 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -881,7 +884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED9FB838-1F75-4E32-A7BC-C2D3C0896BE2}">
-  <dimension ref="B2:P460"/>
+  <dimension ref="B2:P457"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
@@ -945,13 +948,13 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -961,55 +964,55 @@
     </row>
     <row r="5" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
-        <v>46252</v>
+        <v>46274</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1">
-        <v>23280286</v>
+        <v>24111158</v>
       </c>
       <c r="J5" s="1">
         <v>23280286</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>12</v>
+      <c r="K5" s="11" t="s">
+        <v>19</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
-        <v>46253</v>
+        <v>46274</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="1">
-        <v>23280289</v>
+        <v>24110892</v>
       </c>
       <c r="J6" s="1">
         <v>23280286</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1018,31 +1021,21 @@
       <c r="P6" s="4"/>
     </row>
     <row r="7" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
-        <v>46254</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="1">
-        <v>23280346</v>
-      </c>
-      <c r="J7" s="1">
-        <v>23280286</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
     </row>
     <row r="8" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
@@ -1054,12 +1047,12 @@
       <c r="H8" s="4"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
     </row>
     <row r="9" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
@@ -1071,12 +1064,12 @@
       <c r="H9" s="4"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
     </row>
     <row r="10" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -1088,12 +1081,12 @@
       <c r="H10" s="4"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
     </row>
     <row r="11" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
@@ -1105,12 +1098,12 @@
       <c r="H11" s="4"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
@@ -1122,12 +1115,12 @@
       <c r="H12" s="4"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
     </row>
     <row r="13" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
@@ -1139,12 +1132,12 @@
       <c r="H13" s="4"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
@@ -1156,12 +1149,12 @@
       <c r="H14" s="4"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
     </row>
     <row r="15" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
@@ -1173,12 +1166,12 @@
       <c r="H15" s="4"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
     </row>
     <row r="16" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
@@ -1190,12 +1183,12 @@
       <c r="H16" s="4"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
     </row>
     <row r="17" spans="2:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
@@ -1224,12 +1217,12 @@
       <c r="H18" s="4"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
@@ -8694,1434 +8687,1374 @@
       <c r="O457" s="4"/>
       <c r="P457" s="4"/>
     </row>
-    <row r="458" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B458" s="1"/>
-      <c r="C458" s="4"/>
-      <c r="D458" s="4"/>
-      <c r="E458" s="4"/>
-      <c r="F458" s="4"/>
-      <c r="G458" s="4"/>
-      <c r="H458" s="4"/>
-      <c r="I458" s="1"/>
-      <c r="J458" s="1"/>
-      <c r="K458" s="4"/>
-      <c r="L458" s="4"/>
-      <c r="M458" s="4"/>
-      <c r="N458" s="4"/>
-      <c r="O458" s="4"/>
-      <c r="P458" s="4"/>
-    </row>
-    <row r="459" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B459" s="1"/>
-      <c r="C459" s="4"/>
-      <c r="D459" s="4"/>
-      <c r="E459" s="4"/>
-      <c r="F459" s="4"/>
-      <c r="G459" s="4"/>
-      <c r="H459" s="4"/>
-      <c r="I459" s="1"/>
-      <c r="J459" s="1"/>
-      <c r="K459" s="4"/>
-      <c r="L459" s="4"/>
-      <c r="M459" s="4"/>
-      <c r="N459" s="4"/>
-      <c r="O459" s="4"/>
-      <c r="P459" s="4"/>
-    </row>
-    <row r="460" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B460" s="1"/>
-      <c r="C460" s="4"/>
-      <c r="D460" s="4"/>
-      <c r="E460" s="4"/>
-      <c r="F460" s="4"/>
-      <c r="G460" s="4"/>
-      <c r="H460" s="4"/>
-      <c r="I460" s="1"/>
-      <c r="J460" s="1"/>
-      <c r="K460" s="4"/>
-      <c r="L460" s="4"/>
-      <c r="M460" s="4"/>
-      <c r="N460" s="4"/>
-      <c r="O460" s="4"/>
-      <c r="P460" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="1375">
-    <mergeCell ref="G6:H6"/>
+  <mergeCells count="1366">
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="O2:P3"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G14:H14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="O2:P3"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="K18:P18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="K19:P19"/>
+    <mergeCell ref="K16:P16"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="D3:N3"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="K21:P21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="K22:P22"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="K20:P20"/>
-    <mergeCell ref="K14:P14"/>
-    <mergeCell ref="K15:P15"/>
-    <mergeCell ref="K16:P16"/>
     <mergeCell ref="K17:P17"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
     <mergeCell ref="K11:P11"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="K13:P13"/>
-    <mergeCell ref="K4:P4"/>
-    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="K14:P14"/>
+    <mergeCell ref="K15:P15"/>
     <mergeCell ref="K6:P6"/>
     <mergeCell ref="K7:P7"/>
     <mergeCell ref="K8:P8"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="K5:P5"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K24:P24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="K22:P22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="K23:P23"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="K21:P21"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="K29:P29"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:P26"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="K27:P27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="K23:P23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K24:P24"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="K36:P36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="K37:P37"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="K35:P35"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="K32:P32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="K33:P33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="K29:P29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="K42:P42"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="K43:P43"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="K40:P40"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="K41:P41"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="K38:P38"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="G39:H39"/>
     <mergeCell ref="K39:P39"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="K40:P40"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="K37:P37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="K38:P38"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="K35:P35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="K36:P36"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="K48:P48"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="K49:P49"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="K46:P46"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="K47:P47"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="K44:P44"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="G45:H45"/>
     <mergeCell ref="K45:P45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="K46:P46"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="K43:P43"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="K44:P44"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="K41:P41"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="K42:P42"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="K54:P54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="K55:P55"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="K52:P52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="K53:P53"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="K50:P50"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="G51:H51"/>
     <mergeCell ref="K51:P51"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="K52:P52"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="K49:P49"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="K50:P50"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="K47:P47"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="K48:P48"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="K60:P60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="K61:P61"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K58:P58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="K59:P59"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="K56:P56"/>
     <mergeCell ref="C57:F57"/>
     <mergeCell ref="G57:H57"/>
     <mergeCell ref="K57:P57"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="K58:P58"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="K55:P55"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="K56:P56"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="K53:P53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="K54:P54"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="K66:P66"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="K67:P67"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="K65:P65"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="K62:P62"/>
     <mergeCell ref="C63:F63"/>
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="K63:P63"/>
-    <mergeCell ref="C64:F64"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="K64:P64"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="K61:P61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="K62:P62"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="K59:P59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="K60:P60"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="K72:P72"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="K73:P73"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="K70:P70"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="K71:P71"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="K68:P68"/>
     <mergeCell ref="C69:F69"/>
     <mergeCell ref="G69:H69"/>
     <mergeCell ref="K69:P69"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="K70:P70"/>
-    <mergeCell ref="C67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="K67:P67"/>
-    <mergeCell ref="C68:F68"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="K68:P68"/>
-    <mergeCell ref="C65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="K65:P65"/>
-    <mergeCell ref="C66:F66"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="K66:P66"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="K78:P78"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="K79:P79"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="K76:P76"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="K77:P77"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="K74:P74"/>
     <mergeCell ref="C75:F75"/>
     <mergeCell ref="G75:H75"/>
     <mergeCell ref="K75:P75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="K76:P76"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="K73:P73"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="K74:P74"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="K71:P71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="K72:P72"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="K84:P84"/>
+    <mergeCell ref="C85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="K85:P85"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="K82:P82"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="K83:P83"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="K80:P80"/>
     <mergeCell ref="C81:F81"/>
     <mergeCell ref="G81:H81"/>
     <mergeCell ref="K81:P81"/>
-    <mergeCell ref="C82:F82"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="K82:P82"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="K79:P79"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="K80:P80"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="K77:P77"/>
-    <mergeCell ref="C78:F78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="K78:P78"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="K90:P90"/>
+    <mergeCell ref="C91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="K91:P91"/>
+    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="K88:P88"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="K89:P89"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="K86:P86"/>
     <mergeCell ref="C87:F87"/>
     <mergeCell ref="G87:H87"/>
     <mergeCell ref="K87:P87"/>
-    <mergeCell ref="C88:F88"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="K88:P88"/>
-    <mergeCell ref="C85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="K85:P85"/>
-    <mergeCell ref="C86:F86"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="K86:P86"/>
-    <mergeCell ref="C83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="K83:P83"/>
-    <mergeCell ref="C84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="K84:P84"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="K96:P96"/>
+    <mergeCell ref="C97:F97"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="K97:P97"/>
+    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="K94:P94"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="K95:P95"/>
+    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="K92:P92"/>
     <mergeCell ref="C93:F93"/>
     <mergeCell ref="G93:H93"/>
     <mergeCell ref="K93:P93"/>
-    <mergeCell ref="C94:F94"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="K94:P94"/>
-    <mergeCell ref="C91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="K91:P91"/>
-    <mergeCell ref="C92:F92"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="K92:P92"/>
-    <mergeCell ref="C89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="K89:P89"/>
-    <mergeCell ref="C90:F90"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="K90:P90"/>
+    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="K102:P102"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="K103:P103"/>
+    <mergeCell ref="C100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="K100:P100"/>
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="K101:P101"/>
+    <mergeCell ref="C98:F98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="K98:P98"/>
     <mergeCell ref="C99:F99"/>
     <mergeCell ref="G99:H99"/>
     <mergeCell ref="K99:P99"/>
-    <mergeCell ref="C100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="K100:P100"/>
-    <mergeCell ref="C97:F97"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="K97:P97"/>
-    <mergeCell ref="C98:F98"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="K98:P98"/>
-    <mergeCell ref="C95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="K95:P95"/>
-    <mergeCell ref="C96:F96"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="K96:P96"/>
+    <mergeCell ref="C108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="K108:P108"/>
+    <mergeCell ref="C109:F109"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="K109:P109"/>
+    <mergeCell ref="C106:F106"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="K106:P106"/>
+    <mergeCell ref="C107:F107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="K107:P107"/>
+    <mergeCell ref="C104:F104"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="K104:P104"/>
     <mergeCell ref="C105:F105"/>
     <mergeCell ref="G105:H105"/>
     <mergeCell ref="K105:P105"/>
-    <mergeCell ref="C106:F106"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="K106:P106"/>
-    <mergeCell ref="C103:F103"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="K103:P103"/>
-    <mergeCell ref="C104:F104"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="K104:P104"/>
-    <mergeCell ref="C101:F101"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="K101:P101"/>
-    <mergeCell ref="C102:F102"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="K102:P102"/>
+    <mergeCell ref="C114:F114"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="K114:P114"/>
+    <mergeCell ref="C115:F115"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="K115:P115"/>
+    <mergeCell ref="C112:F112"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="K112:P112"/>
+    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="K113:P113"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="K110:P110"/>
     <mergeCell ref="C111:F111"/>
     <mergeCell ref="G111:H111"/>
     <mergeCell ref="K111:P111"/>
-    <mergeCell ref="C112:F112"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="K112:P112"/>
-    <mergeCell ref="C109:F109"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="K109:P109"/>
-    <mergeCell ref="C110:F110"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="K110:P110"/>
-    <mergeCell ref="C107:F107"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="K107:P107"/>
-    <mergeCell ref="C108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="K108:P108"/>
+    <mergeCell ref="C120:F120"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="K120:P120"/>
+    <mergeCell ref="C121:F121"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="K121:P121"/>
+    <mergeCell ref="C118:F118"/>
+    <mergeCell ref="G118:H118"/>
+    <mergeCell ref="K118:P118"/>
+    <mergeCell ref="C119:F119"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="K119:P119"/>
+    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="K116:P116"/>
     <mergeCell ref="C117:F117"/>
     <mergeCell ref="G117:H117"/>
     <mergeCell ref="K117:P117"/>
-    <mergeCell ref="C118:F118"/>
-    <mergeCell ref="G118:H118"/>
-    <mergeCell ref="K118:P118"/>
-    <mergeCell ref="C115:F115"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="K115:P115"/>
-    <mergeCell ref="C116:F116"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="K116:P116"/>
-    <mergeCell ref="C113:F113"/>
-    <mergeCell ref="G113:H113"/>
-    <mergeCell ref="K113:P113"/>
-    <mergeCell ref="C114:F114"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="K114:P114"/>
+    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="K126:P126"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="K127:P127"/>
+    <mergeCell ref="C124:F124"/>
+    <mergeCell ref="G124:H124"/>
+    <mergeCell ref="K124:P124"/>
+    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="K125:P125"/>
+    <mergeCell ref="C122:F122"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="K122:P122"/>
     <mergeCell ref="C123:F123"/>
     <mergeCell ref="G123:H123"/>
     <mergeCell ref="K123:P123"/>
-    <mergeCell ref="C124:F124"/>
-    <mergeCell ref="G124:H124"/>
-    <mergeCell ref="K124:P124"/>
-    <mergeCell ref="C121:F121"/>
-    <mergeCell ref="G121:H121"/>
-    <mergeCell ref="K121:P121"/>
-    <mergeCell ref="C122:F122"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="K122:P122"/>
-    <mergeCell ref="C119:F119"/>
-    <mergeCell ref="G119:H119"/>
-    <mergeCell ref="K119:P119"/>
-    <mergeCell ref="C120:F120"/>
-    <mergeCell ref="G120:H120"/>
-    <mergeCell ref="K120:P120"/>
+    <mergeCell ref="C132:F132"/>
+    <mergeCell ref="G132:H132"/>
+    <mergeCell ref="K132:P132"/>
+    <mergeCell ref="C133:F133"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="K133:P133"/>
+    <mergeCell ref="C130:F130"/>
+    <mergeCell ref="G130:H130"/>
+    <mergeCell ref="K130:P130"/>
+    <mergeCell ref="C131:F131"/>
+    <mergeCell ref="G131:H131"/>
+    <mergeCell ref="K131:P131"/>
+    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="K128:P128"/>
     <mergeCell ref="C129:F129"/>
     <mergeCell ref="G129:H129"/>
     <mergeCell ref="K129:P129"/>
-    <mergeCell ref="C130:F130"/>
-    <mergeCell ref="G130:H130"/>
-    <mergeCell ref="K130:P130"/>
-    <mergeCell ref="C127:F127"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="K127:P127"/>
-    <mergeCell ref="C128:F128"/>
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="K128:P128"/>
-    <mergeCell ref="C125:F125"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="K125:P125"/>
-    <mergeCell ref="C126:F126"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="K126:P126"/>
+    <mergeCell ref="C138:F138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="K138:P138"/>
+    <mergeCell ref="C139:F139"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="K139:P139"/>
+    <mergeCell ref="C136:F136"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="K136:P136"/>
+    <mergeCell ref="C137:F137"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="K137:P137"/>
+    <mergeCell ref="C134:F134"/>
+    <mergeCell ref="G134:H134"/>
+    <mergeCell ref="K134:P134"/>
     <mergeCell ref="C135:F135"/>
     <mergeCell ref="G135:H135"/>
     <mergeCell ref="K135:P135"/>
-    <mergeCell ref="C136:F136"/>
-    <mergeCell ref="G136:H136"/>
-    <mergeCell ref="K136:P136"/>
-    <mergeCell ref="C133:F133"/>
-    <mergeCell ref="G133:H133"/>
-    <mergeCell ref="K133:P133"/>
-    <mergeCell ref="C134:F134"/>
-    <mergeCell ref="G134:H134"/>
-    <mergeCell ref="K134:P134"/>
-    <mergeCell ref="C131:F131"/>
-    <mergeCell ref="G131:H131"/>
-    <mergeCell ref="K131:P131"/>
-    <mergeCell ref="C132:F132"/>
-    <mergeCell ref="G132:H132"/>
-    <mergeCell ref="K132:P132"/>
+    <mergeCell ref="C144:F144"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="K144:P144"/>
+    <mergeCell ref="C145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="K145:P145"/>
+    <mergeCell ref="C142:F142"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="K142:P142"/>
+    <mergeCell ref="C143:F143"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="K143:P143"/>
+    <mergeCell ref="C140:F140"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="K140:P140"/>
     <mergeCell ref="C141:F141"/>
     <mergeCell ref="G141:H141"/>
     <mergeCell ref="K141:P141"/>
-    <mergeCell ref="C142:F142"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="K142:P142"/>
-    <mergeCell ref="C139:F139"/>
-    <mergeCell ref="G139:H139"/>
-    <mergeCell ref="K139:P139"/>
-    <mergeCell ref="C140:F140"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="K140:P140"/>
-    <mergeCell ref="C137:F137"/>
-    <mergeCell ref="G137:H137"/>
-    <mergeCell ref="K137:P137"/>
-    <mergeCell ref="C138:F138"/>
-    <mergeCell ref="G138:H138"/>
-    <mergeCell ref="K138:P138"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="G150:H150"/>
+    <mergeCell ref="K150:P150"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="K151:P151"/>
+    <mergeCell ref="C148:F148"/>
+    <mergeCell ref="G148:H148"/>
+    <mergeCell ref="K148:P148"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="G149:H149"/>
+    <mergeCell ref="K149:P149"/>
+    <mergeCell ref="C146:F146"/>
+    <mergeCell ref="G146:H146"/>
+    <mergeCell ref="K146:P146"/>
     <mergeCell ref="C147:F147"/>
     <mergeCell ref="G147:H147"/>
     <mergeCell ref="K147:P147"/>
-    <mergeCell ref="C148:F148"/>
-    <mergeCell ref="G148:H148"/>
-    <mergeCell ref="K148:P148"/>
-    <mergeCell ref="C145:F145"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="K145:P145"/>
-    <mergeCell ref="C146:F146"/>
-    <mergeCell ref="G146:H146"/>
-    <mergeCell ref="K146:P146"/>
-    <mergeCell ref="C143:F143"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="K143:P143"/>
-    <mergeCell ref="C144:F144"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="K144:P144"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="G156:H156"/>
+    <mergeCell ref="K156:P156"/>
+    <mergeCell ref="C157:F157"/>
+    <mergeCell ref="G157:H157"/>
+    <mergeCell ref="K157:P157"/>
+    <mergeCell ref="C154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="K154:P154"/>
+    <mergeCell ref="C155:F155"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="K155:P155"/>
+    <mergeCell ref="C152:F152"/>
+    <mergeCell ref="G152:H152"/>
+    <mergeCell ref="K152:P152"/>
     <mergeCell ref="C153:F153"/>
     <mergeCell ref="G153:H153"/>
     <mergeCell ref="K153:P153"/>
-    <mergeCell ref="C154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="K154:P154"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="G151:H151"/>
-    <mergeCell ref="K151:P151"/>
-    <mergeCell ref="C152:F152"/>
-    <mergeCell ref="G152:H152"/>
-    <mergeCell ref="K152:P152"/>
-    <mergeCell ref="C149:F149"/>
-    <mergeCell ref="G149:H149"/>
-    <mergeCell ref="K149:P149"/>
-    <mergeCell ref="C150:F150"/>
-    <mergeCell ref="G150:H150"/>
-    <mergeCell ref="K150:P150"/>
+    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="K162:P162"/>
+    <mergeCell ref="C163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="K163:P163"/>
+    <mergeCell ref="C160:F160"/>
+    <mergeCell ref="G160:H160"/>
+    <mergeCell ref="K160:P160"/>
+    <mergeCell ref="C161:F161"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="K161:P161"/>
+    <mergeCell ref="C158:F158"/>
+    <mergeCell ref="G158:H158"/>
+    <mergeCell ref="K158:P158"/>
     <mergeCell ref="C159:F159"/>
     <mergeCell ref="G159:H159"/>
     <mergeCell ref="K159:P159"/>
-    <mergeCell ref="C160:F160"/>
-    <mergeCell ref="G160:H160"/>
-    <mergeCell ref="K160:P160"/>
-    <mergeCell ref="C157:F157"/>
-    <mergeCell ref="G157:H157"/>
-    <mergeCell ref="K157:P157"/>
-    <mergeCell ref="C158:F158"/>
-    <mergeCell ref="G158:H158"/>
-    <mergeCell ref="K158:P158"/>
-    <mergeCell ref="C155:F155"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="K155:P155"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="G156:H156"/>
-    <mergeCell ref="K156:P156"/>
+    <mergeCell ref="C168:F168"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="K168:P168"/>
+    <mergeCell ref="C169:F169"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="K169:P169"/>
+    <mergeCell ref="C166:F166"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="K166:P166"/>
+    <mergeCell ref="C167:F167"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="K167:P167"/>
+    <mergeCell ref="C164:F164"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="K164:P164"/>
     <mergeCell ref="C165:F165"/>
     <mergeCell ref="G165:H165"/>
     <mergeCell ref="K165:P165"/>
-    <mergeCell ref="C166:F166"/>
-    <mergeCell ref="G166:H166"/>
-    <mergeCell ref="K166:P166"/>
-    <mergeCell ref="C163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="K163:P163"/>
-    <mergeCell ref="C164:F164"/>
-    <mergeCell ref="G164:H164"/>
-    <mergeCell ref="K164:P164"/>
-    <mergeCell ref="C161:F161"/>
-    <mergeCell ref="G161:H161"/>
-    <mergeCell ref="K161:P161"/>
-    <mergeCell ref="C162:F162"/>
-    <mergeCell ref="G162:H162"/>
-    <mergeCell ref="K162:P162"/>
+    <mergeCell ref="C174:F174"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="K174:P174"/>
+    <mergeCell ref="C175:F175"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="K175:P175"/>
+    <mergeCell ref="C172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="K172:P172"/>
+    <mergeCell ref="C173:F173"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="K173:P173"/>
+    <mergeCell ref="C170:F170"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="K170:P170"/>
     <mergeCell ref="C171:F171"/>
     <mergeCell ref="G171:H171"/>
     <mergeCell ref="K171:P171"/>
-    <mergeCell ref="C172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="K172:P172"/>
-    <mergeCell ref="C169:F169"/>
-    <mergeCell ref="G169:H169"/>
-    <mergeCell ref="K169:P169"/>
-    <mergeCell ref="C170:F170"/>
-    <mergeCell ref="G170:H170"/>
-    <mergeCell ref="K170:P170"/>
-    <mergeCell ref="C167:F167"/>
-    <mergeCell ref="G167:H167"/>
-    <mergeCell ref="K167:P167"/>
-    <mergeCell ref="C168:F168"/>
-    <mergeCell ref="G168:H168"/>
-    <mergeCell ref="K168:P168"/>
+    <mergeCell ref="C180:F180"/>
+    <mergeCell ref="G180:H180"/>
+    <mergeCell ref="K180:P180"/>
+    <mergeCell ref="C181:F181"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="K181:P181"/>
+    <mergeCell ref="C178:F178"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="K178:P178"/>
+    <mergeCell ref="C179:F179"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="K179:P179"/>
+    <mergeCell ref="C176:F176"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="K176:P176"/>
     <mergeCell ref="C177:F177"/>
     <mergeCell ref="G177:H177"/>
     <mergeCell ref="K177:P177"/>
-    <mergeCell ref="C178:F178"/>
-    <mergeCell ref="G178:H178"/>
-    <mergeCell ref="K178:P178"/>
-    <mergeCell ref="C175:F175"/>
-    <mergeCell ref="G175:H175"/>
-    <mergeCell ref="K175:P175"/>
-    <mergeCell ref="C176:F176"/>
-    <mergeCell ref="G176:H176"/>
-    <mergeCell ref="K176:P176"/>
-    <mergeCell ref="C173:F173"/>
-    <mergeCell ref="G173:H173"/>
-    <mergeCell ref="K173:P173"/>
-    <mergeCell ref="C174:F174"/>
-    <mergeCell ref="G174:H174"/>
-    <mergeCell ref="K174:P174"/>
+    <mergeCell ref="C186:F186"/>
+    <mergeCell ref="G186:H186"/>
+    <mergeCell ref="K186:P186"/>
+    <mergeCell ref="C187:F187"/>
+    <mergeCell ref="G187:H187"/>
+    <mergeCell ref="K187:P187"/>
+    <mergeCell ref="C184:F184"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="K184:P184"/>
+    <mergeCell ref="C185:F185"/>
+    <mergeCell ref="G185:H185"/>
+    <mergeCell ref="K185:P185"/>
+    <mergeCell ref="C182:F182"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="K182:P182"/>
     <mergeCell ref="C183:F183"/>
     <mergeCell ref="G183:H183"/>
     <mergeCell ref="K183:P183"/>
-    <mergeCell ref="C184:F184"/>
-    <mergeCell ref="G184:H184"/>
-    <mergeCell ref="K184:P184"/>
-    <mergeCell ref="C181:F181"/>
-    <mergeCell ref="G181:H181"/>
-    <mergeCell ref="K181:P181"/>
-    <mergeCell ref="C182:F182"/>
-    <mergeCell ref="G182:H182"/>
-    <mergeCell ref="K182:P182"/>
-    <mergeCell ref="C179:F179"/>
-    <mergeCell ref="G179:H179"/>
-    <mergeCell ref="K179:P179"/>
-    <mergeCell ref="C180:F180"/>
-    <mergeCell ref="G180:H180"/>
-    <mergeCell ref="K180:P180"/>
+    <mergeCell ref="C192:F192"/>
+    <mergeCell ref="G192:H192"/>
+    <mergeCell ref="K192:P192"/>
+    <mergeCell ref="C193:F193"/>
+    <mergeCell ref="G193:H193"/>
+    <mergeCell ref="K193:P193"/>
+    <mergeCell ref="C190:F190"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="K190:P190"/>
+    <mergeCell ref="C191:F191"/>
+    <mergeCell ref="G191:H191"/>
+    <mergeCell ref="K191:P191"/>
+    <mergeCell ref="C188:F188"/>
+    <mergeCell ref="G188:H188"/>
+    <mergeCell ref="K188:P188"/>
     <mergeCell ref="C189:F189"/>
     <mergeCell ref="G189:H189"/>
     <mergeCell ref="K189:P189"/>
-    <mergeCell ref="C190:F190"/>
-    <mergeCell ref="G190:H190"/>
-    <mergeCell ref="K190:P190"/>
-    <mergeCell ref="C187:F187"/>
-    <mergeCell ref="G187:H187"/>
-    <mergeCell ref="K187:P187"/>
-    <mergeCell ref="C188:F188"/>
-    <mergeCell ref="G188:H188"/>
-    <mergeCell ref="K188:P188"/>
-    <mergeCell ref="C185:F185"/>
-    <mergeCell ref="G185:H185"/>
-    <mergeCell ref="K185:P185"/>
-    <mergeCell ref="C186:F186"/>
-    <mergeCell ref="G186:H186"/>
-    <mergeCell ref="K186:P186"/>
+    <mergeCell ref="C198:F198"/>
+    <mergeCell ref="G198:H198"/>
+    <mergeCell ref="K198:P198"/>
+    <mergeCell ref="C199:F199"/>
+    <mergeCell ref="G199:H199"/>
+    <mergeCell ref="K199:P199"/>
+    <mergeCell ref="C196:F196"/>
+    <mergeCell ref="G196:H196"/>
+    <mergeCell ref="K196:P196"/>
+    <mergeCell ref="C197:F197"/>
+    <mergeCell ref="G197:H197"/>
+    <mergeCell ref="K197:P197"/>
+    <mergeCell ref="C194:F194"/>
+    <mergeCell ref="G194:H194"/>
+    <mergeCell ref="K194:P194"/>
     <mergeCell ref="C195:F195"/>
     <mergeCell ref="G195:H195"/>
     <mergeCell ref="K195:P195"/>
-    <mergeCell ref="C196:F196"/>
-    <mergeCell ref="G196:H196"/>
-    <mergeCell ref="K196:P196"/>
-    <mergeCell ref="C193:F193"/>
-    <mergeCell ref="G193:H193"/>
-    <mergeCell ref="K193:P193"/>
-    <mergeCell ref="C194:F194"/>
-    <mergeCell ref="G194:H194"/>
-    <mergeCell ref="K194:P194"/>
-    <mergeCell ref="C191:F191"/>
-    <mergeCell ref="G191:H191"/>
-    <mergeCell ref="K191:P191"/>
-    <mergeCell ref="C192:F192"/>
-    <mergeCell ref="G192:H192"/>
-    <mergeCell ref="K192:P192"/>
+    <mergeCell ref="C204:F204"/>
+    <mergeCell ref="G204:H204"/>
+    <mergeCell ref="K204:P204"/>
+    <mergeCell ref="C205:F205"/>
+    <mergeCell ref="G205:H205"/>
+    <mergeCell ref="K205:P205"/>
+    <mergeCell ref="C202:F202"/>
+    <mergeCell ref="G202:H202"/>
+    <mergeCell ref="K202:P202"/>
+    <mergeCell ref="C203:F203"/>
+    <mergeCell ref="G203:H203"/>
+    <mergeCell ref="K203:P203"/>
+    <mergeCell ref="C200:F200"/>
+    <mergeCell ref="G200:H200"/>
+    <mergeCell ref="K200:P200"/>
     <mergeCell ref="C201:F201"/>
     <mergeCell ref="G201:H201"/>
     <mergeCell ref="K201:P201"/>
-    <mergeCell ref="C202:F202"/>
-    <mergeCell ref="G202:H202"/>
-    <mergeCell ref="K202:P202"/>
-    <mergeCell ref="C199:F199"/>
-    <mergeCell ref="G199:H199"/>
-    <mergeCell ref="K199:P199"/>
-    <mergeCell ref="C200:F200"/>
-    <mergeCell ref="G200:H200"/>
-    <mergeCell ref="K200:P200"/>
-    <mergeCell ref="C197:F197"/>
-    <mergeCell ref="G197:H197"/>
-    <mergeCell ref="K197:P197"/>
-    <mergeCell ref="C198:F198"/>
-    <mergeCell ref="G198:H198"/>
-    <mergeCell ref="K198:P198"/>
+    <mergeCell ref="C210:F210"/>
+    <mergeCell ref="G210:H210"/>
+    <mergeCell ref="K210:P210"/>
+    <mergeCell ref="C211:F211"/>
+    <mergeCell ref="G211:H211"/>
+    <mergeCell ref="K211:P211"/>
+    <mergeCell ref="C208:F208"/>
+    <mergeCell ref="G208:H208"/>
+    <mergeCell ref="K208:P208"/>
+    <mergeCell ref="C209:F209"/>
+    <mergeCell ref="G209:H209"/>
+    <mergeCell ref="K209:P209"/>
+    <mergeCell ref="C206:F206"/>
+    <mergeCell ref="G206:H206"/>
+    <mergeCell ref="K206:P206"/>
     <mergeCell ref="C207:F207"/>
     <mergeCell ref="G207:H207"/>
     <mergeCell ref="K207:P207"/>
-    <mergeCell ref="C208:F208"/>
-    <mergeCell ref="G208:H208"/>
-    <mergeCell ref="K208:P208"/>
-    <mergeCell ref="C205:F205"/>
-    <mergeCell ref="G205:H205"/>
-    <mergeCell ref="K205:P205"/>
-    <mergeCell ref="C206:F206"/>
-    <mergeCell ref="G206:H206"/>
-    <mergeCell ref="K206:P206"/>
-    <mergeCell ref="C203:F203"/>
-    <mergeCell ref="G203:H203"/>
-    <mergeCell ref="K203:P203"/>
-    <mergeCell ref="C204:F204"/>
-    <mergeCell ref="G204:H204"/>
-    <mergeCell ref="K204:P204"/>
+    <mergeCell ref="C216:F216"/>
+    <mergeCell ref="G216:H216"/>
+    <mergeCell ref="K216:P216"/>
+    <mergeCell ref="C217:F217"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="K217:P217"/>
+    <mergeCell ref="C214:F214"/>
+    <mergeCell ref="G214:H214"/>
+    <mergeCell ref="K214:P214"/>
+    <mergeCell ref="C215:F215"/>
+    <mergeCell ref="G215:H215"/>
+    <mergeCell ref="K215:P215"/>
+    <mergeCell ref="C212:F212"/>
+    <mergeCell ref="G212:H212"/>
+    <mergeCell ref="K212:P212"/>
     <mergeCell ref="C213:F213"/>
     <mergeCell ref="G213:H213"/>
     <mergeCell ref="K213:P213"/>
-    <mergeCell ref="C214:F214"/>
-    <mergeCell ref="G214:H214"/>
-    <mergeCell ref="K214:P214"/>
-    <mergeCell ref="C211:F211"/>
-    <mergeCell ref="G211:H211"/>
-    <mergeCell ref="K211:P211"/>
-    <mergeCell ref="C212:F212"/>
-    <mergeCell ref="G212:H212"/>
-    <mergeCell ref="K212:P212"/>
-    <mergeCell ref="C209:F209"/>
-    <mergeCell ref="G209:H209"/>
-    <mergeCell ref="K209:P209"/>
-    <mergeCell ref="C210:F210"/>
-    <mergeCell ref="G210:H210"/>
-    <mergeCell ref="K210:P210"/>
+    <mergeCell ref="C222:F222"/>
+    <mergeCell ref="G222:H222"/>
+    <mergeCell ref="K222:P222"/>
+    <mergeCell ref="C223:F223"/>
+    <mergeCell ref="G223:H223"/>
+    <mergeCell ref="K223:P223"/>
+    <mergeCell ref="C220:F220"/>
+    <mergeCell ref="G220:H220"/>
+    <mergeCell ref="K220:P220"/>
+    <mergeCell ref="C221:F221"/>
+    <mergeCell ref="G221:H221"/>
+    <mergeCell ref="K221:P221"/>
+    <mergeCell ref="C218:F218"/>
+    <mergeCell ref="G218:H218"/>
+    <mergeCell ref="K218:P218"/>
     <mergeCell ref="C219:F219"/>
     <mergeCell ref="G219:H219"/>
     <mergeCell ref="K219:P219"/>
-    <mergeCell ref="C220:F220"/>
-    <mergeCell ref="G220:H220"/>
-    <mergeCell ref="K220:P220"/>
-    <mergeCell ref="C217:F217"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="K217:P217"/>
-    <mergeCell ref="C218:F218"/>
-    <mergeCell ref="G218:H218"/>
-    <mergeCell ref="K218:P218"/>
-    <mergeCell ref="C215:F215"/>
-    <mergeCell ref="G215:H215"/>
-    <mergeCell ref="K215:P215"/>
-    <mergeCell ref="C216:F216"/>
-    <mergeCell ref="G216:H216"/>
-    <mergeCell ref="K216:P216"/>
+    <mergeCell ref="C228:F228"/>
+    <mergeCell ref="G228:H228"/>
+    <mergeCell ref="K228:P228"/>
+    <mergeCell ref="C229:F229"/>
+    <mergeCell ref="G229:H229"/>
+    <mergeCell ref="K229:P229"/>
+    <mergeCell ref="C226:F226"/>
+    <mergeCell ref="G226:H226"/>
+    <mergeCell ref="K226:P226"/>
+    <mergeCell ref="C227:F227"/>
+    <mergeCell ref="G227:H227"/>
+    <mergeCell ref="K227:P227"/>
+    <mergeCell ref="C224:F224"/>
+    <mergeCell ref="G224:H224"/>
+    <mergeCell ref="K224:P224"/>
     <mergeCell ref="C225:F225"/>
     <mergeCell ref="G225:H225"/>
     <mergeCell ref="K225:P225"/>
-    <mergeCell ref="C226:F226"/>
-    <mergeCell ref="G226:H226"/>
-    <mergeCell ref="K226:P226"/>
-    <mergeCell ref="C223:F223"/>
-    <mergeCell ref="G223:H223"/>
-    <mergeCell ref="K223:P223"/>
-    <mergeCell ref="C224:F224"/>
-    <mergeCell ref="G224:H224"/>
-    <mergeCell ref="K224:P224"/>
-    <mergeCell ref="C221:F221"/>
-    <mergeCell ref="G221:H221"/>
-    <mergeCell ref="K221:P221"/>
-    <mergeCell ref="C222:F222"/>
-    <mergeCell ref="G222:H222"/>
-    <mergeCell ref="K222:P222"/>
+    <mergeCell ref="C234:F234"/>
+    <mergeCell ref="G234:H234"/>
+    <mergeCell ref="K234:P234"/>
+    <mergeCell ref="C235:F235"/>
+    <mergeCell ref="G235:H235"/>
+    <mergeCell ref="K235:P235"/>
+    <mergeCell ref="C232:F232"/>
+    <mergeCell ref="G232:H232"/>
+    <mergeCell ref="K232:P232"/>
+    <mergeCell ref="C233:F233"/>
+    <mergeCell ref="G233:H233"/>
+    <mergeCell ref="K233:P233"/>
+    <mergeCell ref="C230:F230"/>
+    <mergeCell ref="G230:H230"/>
+    <mergeCell ref="K230:P230"/>
     <mergeCell ref="C231:F231"/>
     <mergeCell ref="G231:H231"/>
     <mergeCell ref="K231:P231"/>
-    <mergeCell ref="C232:F232"/>
-    <mergeCell ref="G232:H232"/>
-    <mergeCell ref="K232:P232"/>
-    <mergeCell ref="C229:F229"/>
-    <mergeCell ref="G229:H229"/>
-    <mergeCell ref="K229:P229"/>
-    <mergeCell ref="C230:F230"/>
-    <mergeCell ref="G230:H230"/>
-    <mergeCell ref="K230:P230"/>
-    <mergeCell ref="C227:F227"/>
-    <mergeCell ref="G227:H227"/>
-    <mergeCell ref="K227:P227"/>
-    <mergeCell ref="C228:F228"/>
-    <mergeCell ref="G228:H228"/>
-    <mergeCell ref="K228:P228"/>
+    <mergeCell ref="C240:F240"/>
+    <mergeCell ref="G240:H240"/>
+    <mergeCell ref="K240:P240"/>
+    <mergeCell ref="C241:F241"/>
+    <mergeCell ref="G241:H241"/>
+    <mergeCell ref="K241:P241"/>
+    <mergeCell ref="C238:F238"/>
+    <mergeCell ref="G238:H238"/>
+    <mergeCell ref="K238:P238"/>
+    <mergeCell ref="C239:F239"/>
+    <mergeCell ref="G239:H239"/>
+    <mergeCell ref="K239:P239"/>
+    <mergeCell ref="C236:F236"/>
+    <mergeCell ref="G236:H236"/>
+    <mergeCell ref="K236:P236"/>
     <mergeCell ref="C237:F237"/>
     <mergeCell ref="G237:H237"/>
     <mergeCell ref="K237:P237"/>
-    <mergeCell ref="C238:F238"/>
-    <mergeCell ref="G238:H238"/>
-    <mergeCell ref="K238:P238"/>
-    <mergeCell ref="C235:F235"/>
-    <mergeCell ref="G235:H235"/>
-    <mergeCell ref="K235:P235"/>
-    <mergeCell ref="C236:F236"/>
-    <mergeCell ref="G236:H236"/>
-    <mergeCell ref="K236:P236"/>
-    <mergeCell ref="C233:F233"/>
-    <mergeCell ref="G233:H233"/>
-    <mergeCell ref="K233:P233"/>
-    <mergeCell ref="C234:F234"/>
-    <mergeCell ref="G234:H234"/>
-    <mergeCell ref="K234:P234"/>
+    <mergeCell ref="C246:F246"/>
+    <mergeCell ref="G246:H246"/>
+    <mergeCell ref="K246:P246"/>
+    <mergeCell ref="C247:F247"/>
+    <mergeCell ref="G247:H247"/>
+    <mergeCell ref="K247:P247"/>
+    <mergeCell ref="C244:F244"/>
+    <mergeCell ref="G244:H244"/>
+    <mergeCell ref="K244:P244"/>
+    <mergeCell ref="C245:F245"/>
+    <mergeCell ref="G245:H245"/>
+    <mergeCell ref="K245:P245"/>
+    <mergeCell ref="C242:F242"/>
+    <mergeCell ref="G242:H242"/>
+    <mergeCell ref="K242:P242"/>
     <mergeCell ref="C243:F243"/>
     <mergeCell ref="G243:H243"/>
     <mergeCell ref="K243:P243"/>
-    <mergeCell ref="C244:F244"/>
-    <mergeCell ref="G244:H244"/>
-    <mergeCell ref="K244:P244"/>
-    <mergeCell ref="C241:F241"/>
-    <mergeCell ref="G241:H241"/>
-    <mergeCell ref="K241:P241"/>
-    <mergeCell ref="C242:F242"/>
-    <mergeCell ref="G242:H242"/>
-    <mergeCell ref="K242:P242"/>
-    <mergeCell ref="C239:F239"/>
-    <mergeCell ref="G239:H239"/>
-    <mergeCell ref="K239:P239"/>
-    <mergeCell ref="C240:F240"/>
-    <mergeCell ref="G240:H240"/>
-    <mergeCell ref="K240:P240"/>
+    <mergeCell ref="C252:F252"/>
+    <mergeCell ref="G252:H252"/>
+    <mergeCell ref="K252:P252"/>
+    <mergeCell ref="C253:F253"/>
+    <mergeCell ref="G253:H253"/>
+    <mergeCell ref="K253:P253"/>
+    <mergeCell ref="C250:F250"/>
+    <mergeCell ref="G250:H250"/>
+    <mergeCell ref="K250:P250"/>
+    <mergeCell ref="C251:F251"/>
+    <mergeCell ref="G251:H251"/>
+    <mergeCell ref="K251:P251"/>
+    <mergeCell ref="C248:F248"/>
+    <mergeCell ref="G248:H248"/>
+    <mergeCell ref="K248:P248"/>
     <mergeCell ref="C249:F249"/>
     <mergeCell ref="G249:H249"/>
     <mergeCell ref="K249:P249"/>
-    <mergeCell ref="C250:F250"/>
-    <mergeCell ref="G250:H250"/>
-    <mergeCell ref="K250:P250"/>
-    <mergeCell ref="C247:F247"/>
-    <mergeCell ref="G247:H247"/>
-    <mergeCell ref="K247:P247"/>
-    <mergeCell ref="C248:F248"/>
-    <mergeCell ref="G248:H248"/>
-    <mergeCell ref="K248:P248"/>
-    <mergeCell ref="C245:F245"/>
-    <mergeCell ref="G245:H245"/>
-    <mergeCell ref="K245:P245"/>
-    <mergeCell ref="C246:F246"/>
-    <mergeCell ref="G246:H246"/>
-    <mergeCell ref="K246:P246"/>
+    <mergeCell ref="C258:F258"/>
+    <mergeCell ref="G258:H258"/>
+    <mergeCell ref="K258:P258"/>
+    <mergeCell ref="C259:F259"/>
+    <mergeCell ref="G259:H259"/>
+    <mergeCell ref="K259:P259"/>
+    <mergeCell ref="C256:F256"/>
+    <mergeCell ref="G256:H256"/>
+    <mergeCell ref="K256:P256"/>
+    <mergeCell ref="C257:F257"/>
+    <mergeCell ref="G257:H257"/>
+    <mergeCell ref="K257:P257"/>
+    <mergeCell ref="C254:F254"/>
+    <mergeCell ref="G254:H254"/>
+    <mergeCell ref="K254:P254"/>
     <mergeCell ref="C255:F255"/>
     <mergeCell ref="G255:H255"/>
     <mergeCell ref="K255:P255"/>
-    <mergeCell ref="C256:F256"/>
-    <mergeCell ref="G256:H256"/>
-    <mergeCell ref="K256:P256"/>
-    <mergeCell ref="C253:F253"/>
-    <mergeCell ref="G253:H253"/>
-    <mergeCell ref="K253:P253"/>
-    <mergeCell ref="C254:F254"/>
-    <mergeCell ref="G254:H254"/>
-    <mergeCell ref="K254:P254"/>
-    <mergeCell ref="C251:F251"/>
-    <mergeCell ref="G251:H251"/>
-    <mergeCell ref="K251:P251"/>
-    <mergeCell ref="C252:F252"/>
-    <mergeCell ref="G252:H252"/>
-    <mergeCell ref="K252:P252"/>
+    <mergeCell ref="C264:F264"/>
+    <mergeCell ref="G264:H264"/>
+    <mergeCell ref="K264:P264"/>
+    <mergeCell ref="C265:F265"/>
+    <mergeCell ref="G265:H265"/>
+    <mergeCell ref="K265:P265"/>
+    <mergeCell ref="C262:F262"/>
+    <mergeCell ref="G262:H262"/>
+    <mergeCell ref="K262:P262"/>
+    <mergeCell ref="C263:F263"/>
+    <mergeCell ref="G263:H263"/>
+    <mergeCell ref="K263:P263"/>
+    <mergeCell ref="C260:F260"/>
+    <mergeCell ref="G260:H260"/>
+    <mergeCell ref="K260:P260"/>
     <mergeCell ref="C261:F261"/>
     <mergeCell ref="G261:H261"/>
     <mergeCell ref="K261:P261"/>
-    <mergeCell ref="C262:F262"/>
-    <mergeCell ref="G262:H262"/>
-    <mergeCell ref="K262:P262"/>
-    <mergeCell ref="C259:F259"/>
-    <mergeCell ref="G259:H259"/>
-    <mergeCell ref="K259:P259"/>
-    <mergeCell ref="C260:F260"/>
-    <mergeCell ref="G260:H260"/>
-    <mergeCell ref="K260:P260"/>
-    <mergeCell ref="C257:F257"/>
-    <mergeCell ref="G257:H257"/>
-    <mergeCell ref="K257:P257"/>
-    <mergeCell ref="C258:F258"/>
-    <mergeCell ref="G258:H258"/>
-    <mergeCell ref="K258:P258"/>
+    <mergeCell ref="C270:F270"/>
+    <mergeCell ref="G270:H270"/>
+    <mergeCell ref="K270:P270"/>
+    <mergeCell ref="C271:F271"/>
+    <mergeCell ref="G271:H271"/>
+    <mergeCell ref="K271:P271"/>
+    <mergeCell ref="C268:F268"/>
+    <mergeCell ref="G268:H268"/>
+    <mergeCell ref="K268:P268"/>
+    <mergeCell ref="C269:F269"/>
+    <mergeCell ref="G269:H269"/>
+    <mergeCell ref="K269:P269"/>
+    <mergeCell ref="C266:F266"/>
+    <mergeCell ref="G266:H266"/>
+    <mergeCell ref="K266:P266"/>
     <mergeCell ref="C267:F267"/>
     <mergeCell ref="G267:H267"/>
     <mergeCell ref="K267:P267"/>
-    <mergeCell ref="C268:F268"/>
-    <mergeCell ref="G268:H268"/>
-    <mergeCell ref="K268:P268"/>
-    <mergeCell ref="C265:F265"/>
-    <mergeCell ref="G265:H265"/>
-    <mergeCell ref="K265:P265"/>
-    <mergeCell ref="C266:F266"/>
-    <mergeCell ref="G266:H266"/>
-    <mergeCell ref="K266:P266"/>
-    <mergeCell ref="C263:F263"/>
-    <mergeCell ref="G263:H263"/>
-    <mergeCell ref="K263:P263"/>
-    <mergeCell ref="C264:F264"/>
-    <mergeCell ref="G264:H264"/>
-    <mergeCell ref="K264:P264"/>
+    <mergeCell ref="C276:F276"/>
+    <mergeCell ref="G276:H276"/>
+    <mergeCell ref="K276:P276"/>
+    <mergeCell ref="C277:F277"/>
+    <mergeCell ref="G277:H277"/>
+    <mergeCell ref="K277:P277"/>
+    <mergeCell ref="C274:F274"/>
+    <mergeCell ref="G274:H274"/>
+    <mergeCell ref="K274:P274"/>
+    <mergeCell ref="C275:F275"/>
+    <mergeCell ref="G275:H275"/>
+    <mergeCell ref="K275:P275"/>
+    <mergeCell ref="C272:F272"/>
+    <mergeCell ref="G272:H272"/>
+    <mergeCell ref="K272:P272"/>
     <mergeCell ref="C273:F273"/>
     <mergeCell ref="G273:H273"/>
     <mergeCell ref="K273:P273"/>
-    <mergeCell ref="C274:F274"/>
-    <mergeCell ref="G274:H274"/>
-    <mergeCell ref="K274:P274"/>
-    <mergeCell ref="C271:F271"/>
-    <mergeCell ref="G271:H271"/>
-    <mergeCell ref="K271:P271"/>
-    <mergeCell ref="C272:F272"/>
-    <mergeCell ref="G272:H272"/>
-    <mergeCell ref="K272:P272"/>
-    <mergeCell ref="C269:F269"/>
-    <mergeCell ref="G269:H269"/>
-    <mergeCell ref="K269:P269"/>
-    <mergeCell ref="C270:F270"/>
-    <mergeCell ref="G270:H270"/>
-    <mergeCell ref="K270:P270"/>
+    <mergeCell ref="C282:F282"/>
+    <mergeCell ref="G282:H282"/>
+    <mergeCell ref="K282:P282"/>
+    <mergeCell ref="C283:F283"/>
+    <mergeCell ref="G283:H283"/>
+    <mergeCell ref="K283:P283"/>
+    <mergeCell ref="C280:F280"/>
+    <mergeCell ref="G280:H280"/>
+    <mergeCell ref="K280:P280"/>
+    <mergeCell ref="C281:F281"/>
+    <mergeCell ref="G281:H281"/>
+    <mergeCell ref="K281:P281"/>
+    <mergeCell ref="C278:F278"/>
+    <mergeCell ref="G278:H278"/>
+    <mergeCell ref="K278:P278"/>
     <mergeCell ref="C279:F279"/>
     <mergeCell ref="G279:H279"/>
     <mergeCell ref="K279:P279"/>
-    <mergeCell ref="C280:F280"/>
-    <mergeCell ref="G280:H280"/>
-    <mergeCell ref="K280:P280"/>
-    <mergeCell ref="C277:F277"/>
-    <mergeCell ref="G277:H277"/>
-    <mergeCell ref="K277:P277"/>
-    <mergeCell ref="C278:F278"/>
-    <mergeCell ref="G278:H278"/>
-    <mergeCell ref="K278:P278"/>
-    <mergeCell ref="C275:F275"/>
-    <mergeCell ref="G275:H275"/>
-    <mergeCell ref="K275:P275"/>
-    <mergeCell ref="C276:F276"/>
-    <mergeCell ref="G276:H276"/>
-    <mergeCell ref="K276:P276"/>
+    <mergeCell ref="C288:F288"/>
+    <mergeCell ref="G288:H288"/>
+    <mergeCell ref="K288:P288"/>
+    <mergeCell ref="C289:F289"/>
+    <mergeCell ref="G289:H289"/>
+    <mergeCell ref="K289:P289"/>
+    <mergeCell ref="C286:F286"/>
+    <mergeCell ref="G286:H286"/>
+    <mergeCell ref="K286:P286"/>
+    <mergeCell ref="C287:F287"/>
+    <mergeCell ref="G287:H287"/>
+    <mergeCell ref="K287:P287"/>
+    <mergeCell ref="C284:F284"/>
+    <mergeCell ref="G284:H284"/>
+    <mergeCell ref="K284:P284"/>
     <mergeCell ref="C285:F285"/>
     <mergeCell ref="G285:H285"/>
     <mergeCell ref="K285:P285"/>
-    <mergeCell ref="C286:F286"/>
-    <mergeCell ref="G286:H286"/>
-    <mergeCell ref="K286:P286"/>
-    <mergeCell ref="C283:F283"/>
-    <mergeCell ref="G283:H283"/>
-    <mergeCell ref="K283:P283"/>
-    <mergeCell ref="C284:F284"/>
-    <mergeCell ref="G284:H284"/>
-    <mergeCell ref="K284:P284"/>
-    <mergeCell ref="C281:F281"/>
-    <mergeCell ref="G281:H281"/>
-    <mergeCell ref="K281:P281"/>
-    <mergeCell ref="C282:F282"/>
-    <mergeCell ref="G282:H282"/>
-    <mergeCell ref="K282:P282"/>
+    <mergeCell ref="C294:F294"/>
+    <mergeCell ref="G294:H294"/>
+    <mergeCell ref="K294:P294"/>
+    <mergeCell ref="C295:F295"/>
+    <mergeCell ref="G295:H295"/>
+    <mergeCell ref="K295:P295"/>
+    <mergeCell ref="C292:F292"/>
+    <mergeCell ref="G292:H292"/>
+    <mergeCell ref="K292:P292"/>
+    <mergeCell ref="C293:F293"/>
+    <mergeCell ref="G293:H293"/>
+    <mergeCell ref="K293:P293"/>
+    <mergeCell ref="C290:F290"/>
+    <mergeCell ref="G290:H290"/>
+    <mergeCell ref="K290:P290"/>
     <mergeCell ref="C291:F291"/>
     <mergeCell ref="G291:H291"/>
     <mergeCell ref="K291:P291"/>
-    <mergeCell ref="C292:F292"/>
-    <mergeCell ref="G292:H292"/>
-    <mergeCell ref="K292:P292"/>
-    <mergeCell ref="C289:F289"/>
-    <mergeCell ref="G289:H289"/>
-    <mergeCell ref="K289:P289"/>
-    <mergeCell ref="C290:F290"/>
-    <mergeCell ref="G290:H290"/>
-    <mergeCell ref="K290:P290"/>
-    <mergeCell ref="C287:F287"/>
-    <mergeCell ref="G287:H287"/>
-    <mergeCell ref="K287:P287"/>
-    <mergeCell ref="C288:F288"/>
-    <mergeCell ref="G288:H288"/>
-    <mergeCell ref="K288:P288"/>
+    <mergeCell ref="C300:F300"/>
+    <mergeCell ref="G300:H300"/>
+    <mergeCell ref="K300:P300"/>
+    <mergeCell ref="C301:F301"/>
+    <mergeCell ref="G301:H301"/>
+    <mergeCell ref="K301:P301"/>
+    <mergeCell ref="C298:F298"/>
+    <mergeCell ref="G298:H298"/>
+    <mergeCell ref="K298:P298"/>
+    <mergeCell ref="C299:F299"/>
+    <mergeCell ref="G299:H299"/>
+    <mergeCell ref="K299:P299"/>
+    <mergeCell ref="C296:F296"/>
+    <mergeCell ref="G296:H296"/>
+    <mergeCell ref="K296:P296"/>
     <mergeCell ref="C297:F297"/>
     <mergeCell ref="G297:H297"/>
     <mergeCell ref="K297:P297"/>
-    <mergeCell ref="C298:F298"/>
-    <mergeCell ref="G298:H298"/>
-    <mergeCell ref="K298:P298"/>
-    <mergeCell ref="C295:F295"/>
-    <mergeCell ref="G295:H295"/>
-    <mergeCell ref="K295:P295"/>
-    <mergeCell ref="C296:F296"/>
-    <mergeCell ref="G296:H296"/>
-    <mergeCell ref="K296:P296"/>
-    <mergeCell ref="C293:F293"/>
-    <mergeCell ref="G293:H293"/>
-    <mergeCell ref="K293:P293"/>
-    <mergeCell ref="C294:F294"/>
-    <mergeCell ref="G294:H294"/>
-    <mergeCell ref="K294:P294"/>
+    <mergeCell ref="C306:F306"/>
+    <mergeCell ref="G306:H306"/>
+    <mergeCell ref="K306:P306"/>
+    <mergeCell ref="C307:F307"/>
+    <mergeCell ref="G307:H307"/>
+    <mergeCell ref="K307:P307"/>
+    <mergeCell ref="C304:F304"/>
+    <mergeCell ref="G304:H304"/>
+    <mergeCell ref="K304:P304"/>
+    <mergeCell ref="C305:F305"/>
+    <mergeCell ref="G305:H305"/>
+    <mergeCell ref="K305:P305"/>
+    <mergeCell ref="C302:F302"/>
+    <mergeCell ref="G302:H302"/>
+    <mergeCell ref="K302:P302"/>
     <mergeCell ref="C303:F303"/>
     <mergeCell ref="G303:H303"/>
     <mergeCell ref="K303:P303"/>
-    <mergeCell ref="C304:F304"/>
-    <mergeCell ref="G304:H304"/>
-    <mergeCell ref="K304:P304"/>
-    <mergeCell ref="C301:F301"/>
-    <mergeCell ref="G301:H301"/>
-    <mergeCell ref="K301:P301"/>
-    <mergeCell ref="C302:F302"/>
-    <mergeCell ref="G302:H302"/>
-    <mergeCell ref="K302:P302"/>
-    <mergeCell ref="C299:F299"/>
-    <mergeCell ref="G299:H299"/>
-    <mergeCell ref="K299:P299"/>
-    <mergeCell ref="C300:F300"/>
-    <mergeCell ref="G300:H300"/>
-    <mergeCell ref="K300:P300"/>
+    <mergeCell ref="C312:F312"/>
+    <mergeCell ref="G312:H312"/>
+    <mergeCell ref="K312:P312"/>
+    <mergeCell ref="C313:F313"/>
+    <mergeCell ref="G313:H313"/>
+    <mergeCell ref="K313:P313"/>
+    <mergeCell ref="C310:F310"/>
+    <mergeCell ref="G310:H310"/>
+    <mergeCell ref="K310:P310"/>
+    <mergeCell ref="C311:F311"/>
+    <mergeCell ref="G311:H311"/>
+    <mergeCell ref="K311:P311"/>
+    <mergeCell ref="C308:F308"/>
+    <mergeCell ref="G308:H308"/>
+    <mergeCell ref="K308:P308"/>
     <mergeCell ref="C309:F309"/>
     <mergeCell ref="G309:H309"/>
     <mergeCell ref="K309:P309"/>
-    <mergeCell ref="C310:F310"/>
-    <mergeCell ref="G310:H310"/>
-    <mergeCell ref="K310:P310"/>
-    <mergeCell ref="C307:F307"/>
-    <mergeCell ref="G307:H307"/>
-    <mergeCell ref="K307:P307"/>
-    <mergeCell ref="C308:F308"/>
-    <mergeCell ref="G308:H308"/>
-    <mergeCell ref="K308:P308"/>
-    <mergeCell ref="C305:F305"/>
-    <mergeCell ref="G305:H305"/>
-    <mergeCell ref="K305:P305"/>
-    <mergeCell ref="C306:F306"/>
-    <mergeCell ref="G306:H306"/>
-    <mergeCell ref="K306:P306"/>
+    <mergeCell ref="C318:F318"/>
+    <mergeCell ref="G318:H318"/>
+    <mergeCell ref="K318:P318"/>
+    <mergeCell ref="C319:F319"/>
+    <mergeCell ref="G319:H319"/>
+    <mergeCell ref="K319:P319"/>
+    <mergeCell ref="C316:F316"/>
+    <mergeCell ref="G316:H316"/>
+    <mergeCell ref="K316:P316"/>
+    <mergeCell ref="C317:F317"/>
+    <mergeCell ref="G317:H317"/>
+    <mergeCell ref="K317:P317"/>
+    <mergeCell ref="C314:F314"/>
+    <mergeCell ref="G314:H314"/>
+    <mergeCell ref="K314:P314"/>
     <mergeCell ref="C315:F315"/>
     <mergeCell ref="G315:H315"/>
     <mergeCell ref="K315:P315"/>
-    <mergeCell ref="C316:F316"/>
-    <mergeCell ref="G316:H316"/>
-    <mergeCell ref="K316:P316"/>
-    <mergeCell ref="C313:F313"/>
-    <mergeCell ref="G313:H313"/>
-    <mergeCell ref="K313:P313"/>
-    <mergeCell ref="C314:F314"/>
-    <mergeCell ref="G314:H314"/>
-    <mergeCell ref="K314:P314"/>
-    <mergeCell ref="C311:F311"/>
-    <mergeCell ref="G311:H311"/>
-    <mergeCell ref="K311:P311"/>
-    <mergeCell ref="C312:F312"/>
-    <mergeCell ref="G312:H312"/>
-    <mergeCell ref="K312:P312"/>
+    <mergeCell ref="C324:F324"/>
+    <mergeCell ref="G324:H324"/>
+    <mergeCell ref="K324:P324"/>
+    <mergeCell ref="C325:F325"/>
+    <mergeCell ref="G325:H325"/>
+    <mergeCell ref="K325:P325"/>
+    <mergeCell ref="C322:F322"/>
+    <mergeCell ref="G322:H322"/>
+    <mergeCell ref="K322:P322"/>
+    <mergeCell ref="C323:F323"/>
+    <mergeCell ref="G323:H323"/>
+    <mergeCell ref="K323:P323"/>
+    <mergeCell ref="C320:F320"/>
+    <mergeCell ref="G320:H320"/>
+    <mergeCell ref="K320:P320"/>
     <mergeCell ref="C321:F321"/>
     <mergeCell ref="G321:H321"/>
     <mergeCell ref="K321:P321"/>
-    <mergeCell ref="C322:F322"/>
-    <mergeCell ref="G322:H322"/>
-    <mergeCell ref="K322:P322"/>
-    <mergeCell ref="C319:F319"/>
-    <mergeCell ref="G319:H319"/>
-    <mergeCell ref="K319:P319"/>
-    <mergeCell ref="C320:F320"/>
-    <mergeCell ref="G320:H320"/>
-    <mergeCell ref="K320:P320"/>
-    <mergeCell ref="C317:F317"/>
-    <mergeCell ref="G317:H317"/>
-    <mergeCell ref="K317:P317"/>
-    <mergeCell ref="C318:F318"/>
-    <mergeCell ref="G318:H318"/>
-    <mergeCell ref="K318:P318"/>
+    <mergeCell ref="C330:F330"/>
+    <mergeCell ref="G330:H330"/>
+    <mergeCell ref="K330:P330"/>
+    <mergeCell ref="C331:F331"/>
+    <mergeCell ref="G331:H331"/>
+    <mergeCell ref="K331:P331"/>
+    <mergeCell ref="C328:F328"/>
+    <mergeCell ref="G328:H328"/>
+    <mergeCell ref="K328:P328"/>
+    <mergeCell ref="C329:F329"/>
+    <mergeCell ref="G329:H329"/>
+    <mergeCell ref="K329:P329"/>
+    <mergeCell ref="C326:F326"/>
+    <mergeCell ref="G326:H326"/>
+    <mergeCell ref="K326:P326"/>
     <mergeCell ref="C327:F327"/>
     <mergeCell ref="G327:H327"/>
     <mergeCell ref="K327:P327"/>
-    <mergeCell ref="C328:F328"/>
-    <mergeCell ref="G328:H328"/>
-    <mergeCell ref="K328:P328"/>
-    <mergeCell ref="C325:F325"/>
-    <mergeCell ref="G325:H325"/>
-    <mergeCell ref="K325:P325"/>
-    <mergeCell ref="C326:F326"/>
-    <mergeCell ref="G326:H326"/>
-    <mergeCell ref="K326:P326"/>
-    <mergeCell ref="C323:F323"/>
-    <mergeCell ref="G323:H323"/>
-    <mergeCell ref="K323:P323"/>
-    <mergeCell ref="C324:F324"/>
-    <mergeCell ref="G324:H324"/>
-    <mergeCell ref="K324:P324"/>
+    <mergeCell ref="C336:F336"/>
+    <mergeCell ref="G336:H336"/>
+    <mergeCell ref="K336:P336"/>
+    <mergeCell ref="C337:F337"/>
+    <mergeCell ref="G337:H337"/>
+    <mergeCell ref="K337:P337"/>
+    <mergeCell ref="C334:F334"/>
+    <mergeCell ref="G334:H334"/>
+    <mergeCell ref="K334:P334"/>
+    <mergeCell ref="C335:F335"/>
+    <mergeCell ref="G335:H335"/>
+    <mergeCell ref="K335:P335"/>
+    <mergeCell ref="C332:F332"/>
+    <mergeCell ref="G332:H332"/>
+    <mergeCell ref="K332:P332"/>
     <mergeCell ref="C333:F333"/>
     <mergeCell ref="G333:H333"/>
     <mergeCell ref="K333:P333"/>
-    <mergeCell ref="C334:F334"/>
-    <mergeCell ref="G334:H334"/>
-    <mergeCell ref="K334:P334"/>
-    <mergeCell ref="C331:F331"/>
-    <mergeCell ref="G331:H331"/>
-    <mergeCell ref="K331:P331"/>
-    <mergeCell ref="C332:F332"/>
-    <mergeCell ref="G332:H332"/>
-    <mergeCell ref="K332:P332"/>
-    <mergeCell ref="C329:F329"/>
-    <mergeCell ref="G329:H329"/>
-    <mergeCell ref="K329:P329"/>
-    <mergeCell ref="C330:F330"/>
-    <mergeCell ref="G330:H330"/>
-    <mergeCell ref="K330:P330"/>
+    <mergeCell ref="C342:F342"/>
+    <mergeCell ref="G342:H342"/>
+    <mergeCell ref="K342:P342"/>
+    <mergeCell ref="C343:F343"/>
+    <mergeCell ref="G343:H343"/>
+    <mergeCell ref="K343:P343"/>
+    <mergeCell ref="C340:F340"/>
+    <mergeCell ref="G340:H340"/>
+    <mergeCell ref="K340:P340"/>
+    <mergeCell ref="C341:F341"/>
+    <mergeCell ref="G341:H341"/>
+    <mergeCell ref="K341:P341"/>
+    <mergeCell ref="C338:F338"/>
+    <mergeCell ref="G338:H338"/>
+    <mergeCell ref="K338:P338"/>
     <mergeCell ref="C339:F339"/>
     <mergeCell ref="G339:H339"/>
     <mergeCell ref="K339:P339"/>
-    <mergeCell ref="C340:F340"/>
-    <mergeCell ref="G340:H340"/>
-    <mergeCell ref="K340:P340"/>
-    <mergeCell ref="C337:F337"/>
-    <mergeCell ref="G337:H337"/>
-    <mergeCell ref="K337:P337"/>
-    <mergeCell ref="C338:F338"/>
-    <mergeCell ref="G338:H338"/>
-    <mergeCell ref="K338:P338"/>
-    <mergeCell ref="C335:F335"/>
-    <mergeCell ref="G335:H335"/>
-    <mergeCell ref="K335:P335"/>
-    <mergeCell ref="C336:F336"/>
-    <mergeCell ref="G336:H336"/>
-    <mergeCell ref="K336:P336"/>
+    <mergeCell ref="C348:F348"/>
+    <mergeCell ref="G348:H348"/>
+    <mergeCell ref="K348:P348"/>
+    <mergeCell ref="C349:F349"/>
+    <mergeCell ref="G349:H349"/>
+    <mergeCell ref="K349:P349"/>
+    <mergeCell ref="C346:F346"/>
+    <mergeCell ref="G346:H346"/>
+    <mergeCell ref="K346:P346"/>
+    <mergeCell ref="C347:F347"/>
+    <mergeCell ref="G347:H347"/>
+    <mergeCell ref="K347:P347"/>
+    <mergeCell ref="C344:F344"/>
+    <mergeCell ref="G344:H344"/>
+    <mergeCell ref="K344:P344"/>
     <mergeCell ref="C345:F345"/>
     <mergeCell ref="G345:H345"/>
     <mergeCell ref="K345:P345"/>
-    <mergeCell ref="C346:F346"/>
-    <mergeCell ref="G346:H346"/>
-    <mergeCell ref="K346:P346"/>
-    <mergeCell ref="C343:F343"/>
-    <mergeCell ref="G343:H343"/>
-    <mergeCell ref="K343:P343"/>
-    <mergeCell ref="C344:F344"/>
-    <mergeCell ref="G344:H344"/>
-    <mergeCell ref="K344:P344"/>
-    <mergeCell ref="C341:F341"/>
-    <mergeCell ref="G341:H341"/>
-    <mergeCell ref="K341:P341"/>
-    <mergeCell ref="C342:F342"/>
-    <mergeCell ref="G342:H342"/>
-    <mergeCell ref="K342:P342"/>
+    <mergeCell ref="C354:F354"/>
+    <mergeCell ref="G354:H354"/>
+    <mergeCell ref="K354:P354"/>
+    <mergeCell ref="C355:F355"/>
+    <mergeCell ref="G355:H355"/>
+    <mergeCell ref="K355:P355"/>
+    <mergeCell ref="C352:F352"/>
+    <mergeCell ref="G352:H352"/>
+    <mergeCell ref="K352:P352"/>
+    <mergeCell ref="C353:F353"/>
+    <mergeCell ref="G353:H353"/>
+    <mergeCell ref="K353:P353"/>
+    <mergeCell ref="C350:F350"/>
+    <mergeCell ref="G350:H350"/>
+    <mergeCell ref="K350:P350"/>
     <mergeCell ref="C351:F351"/>
     <mergeCell ref="G351:H351"/>
     <mergeCell ref="K351:P351"/>
-    <mergeCell ref="C352:F352"/>
-    <mergeCell ref="G352:H352"/>
-    <mergeCell ref="K352:P352"/>
-    <mergeCell ref="C349:F349"/>
-    <mergeCell ref="G349:H349"/>
-    <mergeCell ref="K349:P349"/>
-    <mergeCell ref="C350:F350"/>
-    <mergeCell ref="G350:H350"/>
-    <mergeCell ref="K350:P350"/>
-    <mergeCell ref="C347:F347"/>
-    <mergeCell ref="G347:H347"/>
-    <mergeCell ref="K347:P347"/>
-    <mergeCell ref="C348:F348"/>
-    <mergeCell ref="G348:H348"/>
-    <mergeCell ref="K348:P348"/>
+    <mergeCell ref="C360:F360"/>
+    <mergeCell ref="G360:H360"/>
+    <mergeCell ref="K360:P360"/>
+    <mergeCell ref="C361:F361"/>
+    <mergeCell ref="G361:H361"/>
+    <mergeCell ref="K361:P361"/>
+    <mergeCell ref="C358:F358"/>
+    <mergeCell ref="G358:H358"/>
+    <mergeCell ref="K358:P358"/>
+    <mergeCell ref="C359:F359"/>
+    <mergeCell ref="G359:H359"/>
+    <mergeCell ref="K359:P359"/>
+    <mergeCell ref="C356:F356"/>
+    <mergeCell ref="G356:H356"/>
+    <mergeCell ref="K356:P356"/>
     <mergeCell ref="C357:F357"/>
     <mergeCell ref="G357:H357"/>
     <mergeCell ref="K357:P357"/>
-    <mergeCell ref="C358:F358"/>
-    <mergeCell ref="G358:H358"/>
-    <mergeCell ref="K358:P358"/>
-    <mergeCell ref="C355:F355"/>
-    <mergeCell ref="G355:H355"/>
-    <mergeCell ref="K355:P355"/>
-    <mergeCell ref="C356:F356"/>
-    <mergeCell ref="G356:H356"/>
-    <mergeCell ref="K356:P356"/>
-    <mergeCell ref="C353:F353"/>
-    <mergeCell ref="G353:H353"/>
-    <mergeCell ref="K353:P353"/>
-    <mergeCell ref="C354:F354"/>
-    <mergeCell ref="G354:H354"/>
-    <mergeCell ref="K354:P354"/>
+    <mergeCell ref="C366:F366"/>
+    <mergeCell ref="G366:H366"/>
+    <mergeCell ref="K366:P366"/>
+    <mergeCell ref="C367:F367"/>
+    <mergeCell ref="G367:H367"/>
+    <mergeCell ref="K367:P367"/>
+    <mergeCell ref="C364:F364"/>
+    <mergeCell ref="G364:H364"/>
+    <mergeCell ref="K364:P364"/>
+    <mergeCell ref="C365:F365"/>
+    <mergeCell ref="G365:H365"/>
+    <mergeCell ref="K365:P365"/>
+    <mergeCell ref="C362:F362"/>
+    <mergeCell ref="G362:H362"/>
+    <mergeCell ref="K362:P362"/>
     <mergeCell ref="C363:F363"/>
     <mergeCell ref="G363:H363"/>
     <mergeCell ref="K363:P363"/>
-    <mergeCell ref="C364:F364"/>
-    <mergeCell ref="G364:H364"/>
-    <mergeCell ref="K364:P364"/>
-    <mergeCell ref="C361:F361"/>
-    <mergeCell ref="G361:H361"/>
-    <mergeCell ref="K361:P361"/>
-    <mergeCell ref="C362:F362"/>
-    <mergeCell ref="G362:H362"/>
-    <mergeCell ref="K362:P362"/>
-    <mergeCell ref="C359:F359"/>
-    <mergeCell ref="G359:H359"/>
-    <mergeCell ref="K359:P359"/>
-    <mergeCell ref="C360:F360"/>
-    <mergeCell ref="G360:H360"/>
-    <mergeCell ref="K360:P360"/>
+    <mergeCell ref="C372:F372"/>
+    <mergeCell ref="G372:H372"/>
+    <mergeCell ref="K372:P372"/>
+    <mergeCell ref="C373:F373"/>
+    <mergeCell ref="G373:H373"/>
+    <mergeCell ref="K373:P373"/>
+    <mergeCell ref="C370:F370"/>
+    <mergeCell ref="G370:H370"/>
+    <mergeCell ref="K370:P370"/>
+    <mergeCell ref="C371:F371"/>
+    <mergeCell ref="G371:H371"/>
+    <mergeCell ref="K371:P371"/>
+    <mergeCell ref="C368:F368"/>
+    <mergeCell ref="G368:H368"/>
+    <mergeCell ref="K368:P368"/>
     <mergeCell ref="C369:F369"/>
     <mergeCell ref="G369:H369"/>
     <mergeCell ref="K369:P369"/>
-    <mergeCell ref="C370:F370"/>
-    <mergeCell ref="G370:H370"/>
-    <mergeCell ref="K370:P370"/>
-    <mergeCell ref="C367:F367"/>
-    <mergeCell ref="G367:H367"/>
-    <mergeCell ref="K367:P367"/>
-    <mergeCell ref="C368:F368"/>
-    <mergeCell ref="G368:H368"/>
-    <mergeCell ref="K368:P368"/>
-    <mergeCell ref="C365:F365"/>
-    <mergeCell ref="G365:H365"/>
-    <mergeCell ref="K365:P365"/>
-    <mergeCell ref="C366:F366"/>
-    <mergeCell ref="G366:H366"/>
-    <mergeCell ref="K366:P366"/>
+    <mergeCell ref="C378:F378"/>
+    <mergeCell ref="G378:H378"/>
+    <mergeCell ref="K378:P378"/>
+    <mergeCell ref="C379:F379"/>
+    <mergeCell ref="G379:H379"/>
+    <mergeCell ref="K379:P379"/>
+    <mergeCell ref="C376:F376"/>
+    <mergeCell ref="G376:H376"/>
+    <mergeCell ref="K376:P376"/>
+    <mergeCell ref="C377:F377"/>
+    <mergeCell ref="G377:H377"/>
+    <mergeCell ref="K377:P377"/>
+    <mergeCell ref="C374:F374"/>
+    <mergeCell ref="G374:H374"/>
+    <mergeCell ref="K374:P374"/>
     <mergeCell ref="C375:F375"/>
     <mergeCell ref="G375:H375"/>
     <mergeCell ref="K375:P375"/>
-    <mergeCell ref="C376:F376"/>
-    <mergeCell ref="G376:H376"/>
-    <mergeCell ref="K376:P376"/>
-    <mergeCell ref="C373:F373"/>
-    <mergeCell ref="G373:H373"/>
-    <mergeCell ref="K373:P373"/>
-    <mergeCell ref="C374:F374"/>
-    <mergeCell ref="G374:H374"/>
-    <mergeCell ref="K374:P374"/>
-    <mergeCell ref="C371:F371"/>
-    <mergeCell ref="G371:H371"/>
-    <mergeCell ref="K371:P371"/>
-    <mergeCell ref="C372:F372"/>
-    <mergeCell ref="G372:H372"/>
-    <mergeCell ref="K372:P372"/>
+    <mergeCell ref="C384:F384"/>
+    <mergeCell ref="G384:H384"/>
+    <mergeCell ref="K384:P384"/>
+    <mergeCell ref="C385:F385"/>
+    <mergeCell ref="G385:H385"/>
+    <mergeCell ref="K385:P385"/>
+    <mergeCell ref="C382:F382"/>
+    <mergeCell ref="G382:H382"/>
+    <mergeCell ref="K382:P382"/>
+    <mergeCell ref="C383:F383"/>
+    <mergeCell ref="G383:H383"/>
+    <mergeCell ref="K383:P383"/>
+    <mergeCell ref="C380:F380"/>
+    <mergeCell ref="G380:H380"/>
+    <mergeCell ref="K380:P380"/>
     <mergeCell ref="C381:F381"/>
     <mergeCell ref="G381:H381"/>
     <mergeCell ref="K381:P381"/>
-    <mergeCell ref="C382:F382"/>
-    <mergeCell ref="G382:H382"/>
-    <mergeCell ref="K382:P382"/>
-    <mergeCell ref="C379:F379"/>
-    <mergeCell ref="G379:H379"/>
-    <mergeCell ref="K379:P379"/>
-    <mergeCell ref="C380:F380"/>
-    <mergeCell ref="G380:H380"/>
-    <mergeCell ref="K380:P380"/>
-    <mergeCell ref="C377:F377"/>
-    <mergeCell ref="G377:H377"/>
-    <mergeCell ref="K377:P377"/>
-    <mergeCell ref="C378:F378"/>
-    <mergeCell ref="G378:H378"/>
-    <mergeCell ref="K378:P378"/>
+    <mergeCell ref="C390:F390"/>
+    <mergeCell ref="G390:H390"/>
+    <mergeCell ref="K390:P390"/>
+    <mergeCell ref="C391:F391"/>
+    <mergeCell ref="G391:H391"/>
+    <mergeCell ref="K391:P391"/>
+    <mergeCell ref="C388:F388"/>
+    <mergeCell ref="G388:H388"/>
+    <mergeCell ref="K388:P388"/>
+    <mergeCell ref="C389:F389"/>
+    <mergeCell ref="G389:H389"/>
+    <mergeCell ref="K389:P389"/>
+    <mergeCell ref="C386:F386"/>
+    <mergeCell ref="G386:H386"/>
+    <mergeCell ref="K386:P386"/>
     <mergeCell ref="C387:F387"/>
     <mergeCell ref="G387:H387"/>
     <mergeCell ref="K387:P387"/>
-    <mergeCell ref="C388:F388"/>
-    <mergeCell ref="G388:H388"/>
-    <mergeCell ref="K388:P388"/>
-    <mergeCell ref="C385:F385"/>
-    <mergeCell ref="G385:H385"/>
-    <mergeCell ref="K385:P385"/>
-    <mergeCell ref="C386:F386"/>
-    <mergeCell ref="G386:H386"/>
-    <mergeCell ref="K386:P386"/>
-    <mergeCell ref="C383:F383"/>
-    <mergeCell ref="G383:H383"/>
-    <mergeCell ref="K383:P383"/>
-    <mergeCell ref="C384:F384"/>
-    <mergeCell ref="G384:H384"/>
-    <mergeCell ref="K384:P384"/>
+    <mergeCell ref="C396:F396"/>
+    <mergeCell ref="G396:H396"/>
+    <mergeCell ref="K396:P396"/>
+    <mergeCell ref="C397:F397"/>
+    <mergeCell ref="G397:H397"/>
+    <mergeCell ref="K397:P397"/>
+    <mergeCell ref="C394:F394"/>
+    <mergeCell ref="G394:H394"/>
+    <mergeCell ref="K394:P394"/>
+    <mergeCell ref="C395:F395"/>
+    <mergeCell ref="G395:H395"/>
+    <mergeCell ref="K395:P395"/>
+    <mergeCell ref="C392:F392"/>
+    <mergeCell ref="G392:H392"/>
+    <mergeCell ref="K392:P392"/>
     <mergeCell ref="C393:F393"/>
     <mergeCell ref="G393:H393"/>
     <mergeCell ref="K393:P393"/>
-    <mergeCell ref="C394:F394"/>
-    <mergeCell ref="G394:H394"/>
-    <mergeCell ref="K394:P394"/>
-    <mergeCell ref="C391:F391"/>
-    <mergeCell ref="G391:H391"/>
-    <mergeCell ref="K391:P391"/>
-    <mergeCell ref="C392:F392"/>
-    <mergeCell ref="G392:H392"/>
-    <mergeCell ref="K392:P392"/>
-    <mergeCell ref="C389:F389"/>
-    <mergeCell ref="G389:H389"/>
-    <mergeCell ref="K389:P389"/>
-    <mergeCell ref="C390:F390"/>
-    <mergeCell ref="G390:H390"/>
-    <mergeCell ref="K390:P390"/>
+    <mergeCell ref="C402:F402"/>
+    <mergeCell ref="G402:H402"/>
+    <mergeCell ref="K402:P402"/>
+    <mergeCell ref="C403:F403"/>
+    <mergeCell ref="G403:H403"/>
+    <mergeCell ref="K403:P403"/>
+    <mergeCell ref="C400:F400"/>
+    <mergeCell ref="G400:H400"/>
+    <mergeCell ref="K400:P400"/>
+    <mergeCell ref="C401:F401"/>
+    <mergeCell ref="G401:H401"/>
+    <mergeCell ref="K401:P401"/>
+    <mergeCell ref="C398:F398"/>
+    <mergeCell ref="G398:H398"/>
+    <mergeCell ref="K398:P398"/>
     <mergeCell ref="C399:F399"/>
     <mergeCell ref="G399:H399"/>
     <mergeCell ref="K399:P399"/>
-    <mergeCell ref="C400:F400"/>
-    <mergeCell ref="G400:H400"/>
-    <mergeCell ref="K400:P400"/>
-    <mergeCell ref="C397:F397"/>
-    <mergeCell ref="G397:H397"/>
-    <mergeCell ref="K397:P397"/>
-    <mergeCell ref="C398:F398"/>
-    <mergeCell ref="G398:H398"/>
-    <mergeCell ref="K398:P398"/>
-    <mergeCell ref="C395:F395"/>
-    <mergeCell ref="G395:H395"/>
-    <mergeCell ref="K395:P395"/>
-    <mergeCell ref="C396:F396"/>
-    <mergeCell ref="G396:H396"/>
-    <mergeCell ref="K396:P396"/>
+    <mergeCell ref="C408:F408"/>
+    <mergeCell ref="G408:H408"/>
+    <mergeCell ref="K408:P408"/>
+    <mergeCell ref="C409:F409"/>
+    <mergeCell ref="G409:H409"/>
+    <mergeCell ref="K409:P409"/>
+    <mergeCell ref="C406:F406"/>
+    <mergeCell ref="G406:H406"/>
+    <mergeCell ref="K406:P406"/>
+    <mergeCell ref="C407:F407"/>
+    <mergeCell ref="G407:H407"/>
+    <mergeCell ref="K407:P407"/>
+    <mergeCell ref="C404:F404"/>
+    <mergeCell ref="G404:H404"/>
+    <mergeCell ref="K404:P404"/>
     <mergeCell ref="C405:F405"/>
     <mergeCell ref="G405:H405"/>
     <mergeCell ref="K405:P405"/>
-    <mergeCell ref="C406:F406"/>
-    <mergeCell ref="G406:H406"/>
-    <mergeCell ref="K406:P406"/>
-    <mergeCell ref="C403:F403"/>
-    <mergeCell ref="G403:H403"/>
-    <mergeCell ref="K403:P403"/>
-    <mergeCell ref="C404:F404"/>
-    <mergeCell ref="G404:H404"/>
-    <mergeCell ref="K404:P404"/>
-    <mergeCell ref="C401:F401"/>
-    <mergeCell ref="G401:H401"/>
-    <mergeCell ref="K401:P401"/>
-    <mergeCell ref="C402:F402"/>
-    <mergeCell ref="G402:H402"/>
-    <mergeCell ref="K402:P402"/>
+    <mergeCell ref="C414:F414"/>
+    <mergeCell ref="G414:H414"/>
+    <mergeCell ref="K414:P414"/>
+    <mergeCell ref="C415:F415"/>
+    <mergeCell ref="G415:H415"/>
+    <mergeCell ref="K415:P415"/>
+    <mergeCell ref="C412:F412"/>
+    <mergeCell ref="G412:H412"/>
+    <mergeCell ref="K412:P412"/>
+    <mergeCell ref="C413:F413"/>
+    <mergeCell ref="G413:H413"/>
+    <mergeCell ref="K413:P413"/>
+    <mergeCell ref="C410:F410"/>
+    <mergeCell ref="G410:H410"/>
+    <mergeCell ref="K410:P410"/>
     <mergeCell ref="C411:F411"/>
     <mergeCell ref="G411:H411"/>
     <mergeCell ref="K411:P411"/>
-    <mergeCell ref="C412:F412"/>
-    <mergeCell ref="G412:H412"/>
-    <mergeCell ref="K412:P412"/>
-    <mergeCell ref="C409:F409"/>
-    <mergeCell ref="G409:H409"/>
-    <mergeCell ref="K409:P409"/>
-    <mergeCell ref="C410:F410"/>
-    <mergeCell ref="G410:H410"/>
-    <mergeCell ref="K410:P410"/>
-    <mergeCell ref="C407:F407"/>
-    <mergeCell ref="G407:H407"/>
-    <mergeCell ref="K407:P407"/>
-    <mergeCell ref="C408:F408"/>
-    <mergeCell ref="G408:H408"/>
-    <mergeCell ref="K408:P408"/>
+    <mergeCell ref="C420:F420"/>
+    <mergeCell ref="G420:H420"/>
+    <mergeCell ref="K420:P420"/>
+    <mergeCell ref="C421:F421"/>
+    <mergeCell ref="G421:H421"/>
+    <mergeCell ref="K421:P421"/>
+    <mergeCell ref="C418:F418"/>
+    <mergeCell ref="G418:H418"/>
+    <mergeCell ref="K418:P418"/>
+    <mergeCell ref="C419:F419"/>
+    <mergeCell ref="G419:H419"/>
+    <mergeCell ref="K419:P419"/>
+    <mergeCell ref="C416:F416"/>
+    <mergeCell ref="G416:H416"/>
+    <mergeCell ref="K416:P416"/>
     <mergeCell ref="C417:F417"/>
     <mergeCell ref="G417:H417"/>
     <mergeCell ref="K417:P417"/>
-    <mergeCell ref="C418:F418"/>
-    <mergeCell ref="G418:H418"/>
-    <mergeCell ref="K418:P418"/>
-    <mergeCell ref="C415:F415"/>
-    <mergeCell ref="G415:H415"/>
-    <mergeCell ref="K415:P415"/>
-    <mergeCell ref="C416:F416"/>
-    <mergeCell ref="G416:H416"/>
-    <mergeCell ref="K416:P416"/>
-    <mergeCell ref="C413:F413"/>
-    <mergeCell ref="G413:H413"/>
-    <mergeCell ref="K413:P413"/>
-    <mergeCell ref="C414:F414"/>
-    <mergeCell ref="G414:H414"/>
-    <mergeCell ref="K414:P414"/>
+    <mergeCell ref="C426:F426"/>
+    <mergeCell ref="G426:H426"/>
+    <mergeCell ref="K426:P426"/>
+    <mergeCell ref="C427:F427"/>
+    <mergeCell ref="G427:H427"/>
+    <mergeCell ref="K427:P427"/>
+    <mergeCell ref="C424:F424"/>
+    <mergeCell ref="G424:H424"/>
+    <mergeCell ref="K424:P424"/>
+    <mergeCell ref="C425:F425"/>
+    <mergeCell ref="G425:H425"/>
+    <mergeCell ref="K425:P425"/>
+    <mergeCell ref="C422:F422"/>
+    <mergeCell ref="G422:H422"/>
+    <mergeCell ref="K422:P422"/>
     <mergeCell ref="C423:F423"/>
     <mergeCell ref="G423:H423"/>
     <mergeCell ref="K423:P423"/>
-    <mergeCell ref="C424:F424"/>
-    <mergeCell ref="G424:H424"/>
-    <mergeCell ref="K424:P424"/>
-    <mergeCell ref="C421:F421"/>
-    <mergeCell ref="G421:H421"/>
-    <mergeCell ref="K421:P421"/>
-    <mergeCell ref="C422:F422"/>
-    <mergeCell ref="G422:H422"/>
-    <mergeCell ref="K422:P422"/>
-    <mergeCell ref="C419:F419"/>
-    <mergeCell ref="G419:H419"/>
-    <mergeCell ref="K419:P419"/>
-    <mergeCell ref="C420:F420"/>
-    <mergeCell ref="G420:H420"/>
-    <mergeCell ref="K420:P420"/>
+    <mergeCell ref="C432:F432"/>
+    <mergeCell ref="G432:H432"/>
+    <mergeCell ref="K432:P432"/>
+    <mergeCell ref="C433:F433"/>
+    <mergeCell ref="G433:H433"/>
+    <mergeCell ref="K433:P433"/>
+    <mergeCell ref="C430:F430"/>
+    <mergeCell ref="G430:H430"/>
+    <mergeCell ref="K430:P430"/>
+    <mergeCell ref="C431:F431"/>
+    <mergeCell ref="G431:H431"/>
+    <mergeCell ref="K431:P431"/>
+    <mergeCell ref="C428:F428"/>
+    <mergeCell ref="G428:H428"/>
+    <mergeCell ref="K428:P428"/>
     <mergeCell ref="C429:F429"/>
     <mergeCell ref="G429:H429"/>
     <mergeCell ref="K429:P429"/>
-    <mergeCell ref="C430:F430"/>
-    <mergeCell ref="G430:H430"/>
-    <mergeCell ref="K430:P430"/>
-    <mergeCell ref="C427:F427"/>
-    <mergeCell ref="G427:H427"/>
-    <mergeCell ref="K427:P427"/>
-    <mergeCell ref="C428:F428"/>
-    <mergeCell ref="G428:H428"/>
-    <mergeCell ref="K428:P428"/>
-    <mergeCell ref="C425:F425"/>
-    <mergeCell ref="G425:H425"/>
-    <mergeCell ref="K425:P425"/>
-    <mergeCell ref="C426:F426"/>
-    <mergeCell ref="G426:H426"/>
-    <mergeCell ref="K426:P426"/>
+    <mergeCell ref="C438:F438"/>
+    <mergeCell ref="G438:H438"/>
+    <mergeCell ref="K438:P438"/>
+    <mergeCell ref="C439:F439"/>
+    <mergeCell ref="G439:H439"/>
+    <mergeCell ref="K439:P439"/>
+    <mergeCell ref="C436:F436"/>
+    <mergeCell ref="G436:H436"/>
+    <mergeCell ref="K436:P436"/>
+    <mergeCell ref="C437:F437"/>
+    <mergeCell ref="G437:H437"/>
+    <mergeCell ref="K437:P437"/>
+    <mergeCell ref="C434:F434"/>
+    <mergeCell ref="G434:H434"/>
+    <mergeCell ref="K434:P434"/>
     <mergeCell ref="C435:F435"/>
     <mergeCell ref="G435:H435"/>
     <mergeCell ref="K435:P435"/>
-    <mergeCell ref="C436:F436"/>
-    <mergeCell ref="G436:H436"/>
-    <mergeCell ref="K436:P436"/>
-    <mergeCell ref="C433:F433"/>
-    <mergeCell ref="G433:H433"/>
-    <mergeCell ref="K433:P433"/>
-    <mergeCell ref="C434:F434"/>
-    <mergeCell ref="G434:H434"/>
-    <mergeCell ref="K434:P434"/>
-    <mergeCell ref="C431:F431"/>
-    <mergeCell ref="G431:H431"/>
-    <mergeCell ref="K431:P431"/>
-    <mergeCell ref="C432:F432"/>
-    <mergeCell ref="G432:H432"/>
-    <mergeCell ref="K432:P432"/>
+    <mergeCell ref="C444:F444"/>
+    <mergeCell ref="G444:H444"/>
+    <mergeCell ref="K444:P444"/>
+    <mergeCell ref="C445:F445"/>
+    <mergeCell ref="G445:H445"/>
+    <mergeCell ref="K445:P445"/>
+    <mergeCell ref="C442:F442"/>
+    <mergeCell ref="G442:H442"/>
+    <mergeCell ref="K442:P442"/>
+    <mergeCell ref="C443:F443"/>
+    <mergeCell ref="G443:H443"/>
+    <mergeCell ref="K443:P443"/>
+    <mergeCell ref="C440:F440"/>
+    <mergeCell ref="G440:H440"/>
+    <mergeCell ref="K440:P440"/>
     <mergeCell ref="C441:F441"/>
     <mergeCell ref="G441:H441"/>
     <mergeCell ref="K441:P441"/>
-    <mergeCell ref="C442:F442"/>
-    <mergeCell ref="G442:H442"/>
-    <mergeCell ref="K442:P442"/>
-    <mergeCell ref="C439:F439"/>
-    <mergeCell ref="G439:H439"/>
-    <mergeCell ref="K439:P439"/>
-    <mergeCell ref="C440:F440"/>
-    <mergeCell ref="G440:H440"/>
-    <mergeCell ref="K440:P440"/>
-    <mergeCell ref="C437:F437"/>
-    <mergeCell ref="G437:H437"/>
-    <mergeCell ref="K437:P437"/>
-    <mergeCell ref="C438:F438"/>
-    <mergeCell ref="G438:H438"/>
-    <mergeCell ref="K438:P438"/>
+    <mergeCell ref="C450:F450"/>
+    <mergeCell ref="G450:H450"/>
+    <mergeCell ref="K450:P450"/>
+    <mergeCell ref="C451:F451"/>
+    <mergeCell ref="G451:H451"/>
+    <mergeCell ref="K451:P451"/>
+    <mergeCell ref="C448:F448"/>
+    <mergeCell ref="G448:H448"/>
+    <mergeCell ref="K448:P448"/>
+    <mergeCell ref="C449:F449"/>
+    <mergeCell ref="G449:H449"/>
+    <mergeCell ref="K449:P449"/>
+    <mergeCell ref="C446:F446"/>
+    <mergeCell ref="G446:H446"/>
+    <mergeCell ref="K446:P446"/>
     <mergeCell ref="C447:F447"/>
     <mergeCell ref="G447:H447"/>
     <mergeCell ref="K447:P447"/>
-    <mergeCell ref="C448:F448"/>
-    <mergeCell ref="G448:H448"/>
-    <mergeCell ref="K448:P448"/>
-    <mergeCell ref="C445:F445"/>
-    <mergeCell ref="G445:H445"/>
-    <mergeCell ref="K445:P445"/>
-    <mergeCell ref="C446:F446"/>
-    <mergeCell ref="G446:H446"/>
-    <mergeCell ref="K446:P446"/>
-    <mergeCell ref="C443:F443"/>
-    <mergeCell ref="G443:H443"/>
-    <mergeCell ref="K443:P443"/>
-    <mergeCell ref="C444:F444"/>
-    <mergeCell ref="G444:H444"/>
-    <mergeCell ref="K444:P444"/>
+    <mergeCell ref="C456:F456"/>
+    <mergeCell ref="G456:H456"/>
+    <mergeCell ref="K456:P456"/>
+    <mergeCell ref="C457:F457"/>
+    <mergeCell ref="G457:H457"/>
+    <mergeCell ref="K457:P457"/>
+    <mergeCell ref="C454:F454"/>
+    <mergeCell ref="G454:H454"/>
+    <mergeCell ref="K454:P454"/>
+    <mergeCell ref="C455:F455"/>
+    <mergeCell ref="G455:H455"/>
+    <mergeCell ref="K455:P455"/>
+    <mergeCell ref="C452:F452"/>
+    <mergeCell ref="G452:H452"/>
+    <mergeCell ref="K452:P452"/>
     <mergeCell ref="C453:F453"/>
     <mergeCell ref="G453:H453"/>
     <mergeCell ref="K453:P453"/>
-    <mergeCell ref="C454:F454"/>
-    <mergeCell ref="G454:H454"/>
-    <mergeCell ref="K454:P454"/>
-    <mergeCell ref="C451:F451"/>
-    <mergeCell ref="G451:H451"/>
-    <mergeCell ref="K451:P451"/>
-    <mergeCell ref="C452:F452"/>
-    <mergeCell ref="G452:H452"/>
-    <mergeCell ref="K452:P452"/>
-    <mergeCell ref="C449:F449"/>
-    <mergeCell ref="G449:H449"/>
-    <mergeCell ref="K449:P449"/>
-    <mergeCell ref="C450:F450"/>
-    <mergeCell ref="G450:H450"/>
-    <mergeCell ref="K450:P450"/>
-    <mergeCell ref="C459:F459"/>
-    <mergeCell ref="G459:H459"/>
-    <mergeCell ref="K459:P459"/>
-    <mergeCell ref="C460:F460"/>
-    <mergeCell ref="G460:H460"/>
-    <mergeCell ref="K460:P460"/>
-    <mergeCell ref="C457:F457"/>
-    <mergeCell ref="G457:H457"/>
-    <mergeCell ref="K457:P457"/>
-    <mergeCell ref="C458:F458"/>
-    <mergeCell ref="G458:H458"/>
-    <mergeCell ref="K458:P458"/>
-    <mergeCell ref="C455:F455"/>
-    <mergeCell ref="G455:H455"/>
-    <mergeCell ref="K455:P455"/>
-    <mergeCell ref="C456:F456"/>
-    <mergeCell ref="G456:H456"/>
-    <mergeCell ref="K456:P456"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10193,13 +10126,13 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -10218,14 +10151,14 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1">
         <v>23280286</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -19417,13 +19350,13 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -19442,14 +19375,14 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1">
         <v>23280286</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -28641,13 +28574,13 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -28666,14 +28599,14 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1">
         <v>23280286</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -37865,13 +37798,13 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -37890,14 +37823,14 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1">
         <v>23280286</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
